--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,210 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124799557</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rötmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>778081</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7191937</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124799558</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rötmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>778074</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7191941</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124799557</v>
+        <v>124799558</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778081</v>
+        <v>778074</v>
       </c>
       <c r="R3" t="n">
-        <v>7191937</v>
+        <v>7191941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124799558</v>
+        <v>124799557</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778074</v>
+        <v>778081</v>
       </c>
       <c r="R4" t="n">
-        <v>7191941</v>
+        <v>7191937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +978,228 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125014012</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>778079</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7191921</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125013964</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>778068</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7191944</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124799558</v>
+        <v>124799557</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778074</v>
+        <v>778081</v>
       </c>
       <c r="R3" t="n">
-        <v>7191941</v>
+        <v>7191937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124799557</v>
+        <v>124799558</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778081</v>
+        <v>778074</v>
       </c>
       <c r="R4" t="n">
-        <v>7191937</v>
+        <v>7191941</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125014012</v>
+        <v>125013964</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778079</v>
+        <v>778068</v>
       </c>
       <c r="R5" t="n">
-        <v>7191921</v>
+        <v>7191944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125013964</v>
+        <v>125014012</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778068</v>
+        <v>778079</v>
       </c>
       <c r="R6" t="n">
-        <v>7191944</v>
+        <v>7191921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125013964</v>
+        <v>125014012</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778068</v>
+        <v>778079</v>
       </c>
       <c r="R5" t="n">
-        <v>7191944</v>
+        <v>7191921</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125014012</v>
+        <v>125013964</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778079</v>
+        <v>778068</v>
       </c>
       <c r="R6" t="n">
-        <v>7191921</v>
+        <v>7191944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125014012</v>
+        <v>125013964</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778079</v>
+        <v>778068</v>
       </c>
       <c r="R5" t="n">
-        <v>7191921</v>
+        <v>7191944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125013964</v>
+        <v>125014012</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778068</v>
+        <v>778079</v>
       </c>
       <c r="R6" t="n">
-        <v>7191944</v>
+        <v>7191921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124799557</v>
+        <v>124799558</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778081</v>
+        <v>778074</v>
       </c>
       <c r="R3" t="n">
-        <v>7191937</v>
+        <v>7191941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124799558</v>
+        <v>124799557</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778074</v>
+        <v>778081</v>
       </c>
       <c r="R4" t="n">
-        <v>7191941</v>
+        <v>7191937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125014012</v>
+        <v>125013964</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778079</v>
+        <v>778068</v>
       </c>
       <c r="R5" t="n">
-        <v>7191921</v>
+        <v>7191944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125013964</v>
+        <v>125014012</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778068</v>
+        <v>778079</v>
       </c>
       <c r="R6" t="n">
-        <v>7191944</v>
+        <v>7191921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124799558</v>
+        <v>124799557</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778074</v>
+        <v>778081</v>
       </c>
       <c r="R3" t="n">
-        <v>7191941</v>
+        <v>7191937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124799557</v>
+        <v>124799558</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778081</v>
+        <v>778074</v>
       </c>
       <c r="R4" t="n">
-        <v>7191937</v>
+        <v>7191941</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125013964</v>
+        <v>125014012</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778068</v>
+        <v>778079</v>
       </c>
       <c r="R5" t="n">
-        <v>7191944</v>
+        <v>7191921</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125014012</v>
+        <v>125013964</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778079</v>
+        <v>778068</v>
       </c>
       <c r="R6" t="n">
-        <v>7191921</v>
+        <v>7191944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124671089</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124799557</v>
+        <v>124799558</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778081</v>
+        <v>778074</v>
       </c>
       <c r="R3" t="n">
-        <v>7191937</v>
+        <v>7191941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124799558</v>
+        <v>124799557</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778074</v>
+        <v>778081</v>
       </c>
       <c r="R4" t="n">
-        <v>7191941</v>
+        <v>7191937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125014012</v>
+        <v>125013964</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778079</v>
+        <v>778068</v>
       </c>
       <c r="R5" t="n">
-        <v>7191921</v>
+        <v>7191944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125013964</v>
+        <v>125014012</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778068</v>
+        <v>778079</v>
       </c>
       <c r="R6" t="n">
-        <v>7191944</v>
+        <v>7191921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124799558</v>
+        <v>124799557</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778074</v>
+        <v>778081</v>
       </c>
       <c r="R3" t="n">
-        <v>7191941</v>
+        <v>7191937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124799557</v>
+        <v>124799558</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778081</v>
+        <v>778074</v>
       </c>
       <c r="R4" t="n">
-        <v>7191937</v>
+        <v>7191941</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125013964</v>
+        <v>125014012</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778068</v>
+        <v>778079</v>
       </c>
       <c r="R5" t="n">
-        <v>7191944</v>
+        <v>7191921</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125014012</v>
+        <v>125013964</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778079</v>
+        <v>778068</v>
       </c>
       <c r="R6" t="n">
-        <v>7191921</v>
+        <v>7191944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -986,11 +986,6 @@
       <c r="B5" t="n">
         <v>98269</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1096,11 +1091,6 @@
       </c>
       <c r="B6" t="n">
         <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124671089</v>
+        <v>124671087</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778084</v>
+        <v>778140</v>
       </c>
       <c r="R2" t="n">
-        <v>7191928</v>
+        <v>7191913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124799557</v>
+        <v>124671088</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rötmyran, Vb</t>
+          <t>Falkliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778081</v>
+        <v>778096</v>
       </c>
       <c r="R3" t="n">
-        <v>7191937</v>
+        <v>7191916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124799558</v>
+        <v>124671089</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rötmyran, Vb</t>
+          <t>Falkliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778074</v>
+        <v>778084</v>
       </c>
       <c r="R4" t="n">
-        <v>7191941</v>
+        <v>7191928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125014012</v>
+        <v>124799557</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,24 +995,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lundliden, Vb</t>
+          <t>Rötmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778079</v>
+        <v>778081</v>
       </c>
       <c r="R5" t="n">
-        <v>7191921</v>
+        <v>7191937</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,29 +1045,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125013964</v>
+        <v>124799558</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,24 +1092,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lundliden, Vb</t>
+          <t>Rötmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778068</v>
+        <v>778074</v>
       </c>
       <c r="R6" t="n">
-        <v>7191944</v>
+        <v>7191941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1142,445 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125013936</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>778058</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7191907</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125013964</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>778068</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7191944</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125014012</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>778079</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7191921</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125014041</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>778113</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7191912</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8820-2025 artfynd.xlsx
+++ b/artfynd/A 8820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124671087</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124671088</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124671089</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124799557</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124799558</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125013936</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125013964</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125014012</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,8 +1626,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125014041</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>